--- a/tests/realSuite/Piano-Viaggi_Scacchi_18-feb-25_DEF/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Scacchi_18-feb-25_DEF/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,165 +541,195 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC ROVERETO LA VELA Primaria 2°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Corso Bettini 67 - Rovereto</t>
+          <t>Piazzale Achille Leoni - Rovereto</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Via Livenza 1 - Rovereto</t>
+          <t>Corso Bettini 67 - Rovereto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Via Circonvalazione 44 - Tione</t>
+          <t>Via Benacense, 32 - Rovereto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IS CLES PILATI</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Piazza Fiera, Cles</t>
+          <t>Via Livenza 1 - Rovereto</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IS DON MILANI ROVERETO</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Balista 2, Rovereto</t>
+          <t>Via Circonvalazione 44 - Tione</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IS FLORIANI RIVA DEL GARDA</t>
+          <t>IS CLES PILATI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Viale dei Tigli, 43 - Riva del Garda</t>
+          <t>Piazza Fiera, Cles</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IS MAFFEI RIVA DEL GARDA</t>
+          <t>IS DON MILANI ROVERETO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Viale Martiri, Fermata autobus - Riva del Garda</t>
+          <t>Via Balista 2, Rovereto</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS FLORIANI RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Via Monti, n. 1 – Rovereto, Parcheggio di fronte all'Istituto Marconi</t>
+          <t>Viale dei Tigli, 43 - Riva del Garda</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IS MARTINI MEZZOLOMBARDO</t>
+          <t>IS MAFFEI RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Via Perlasca 4, Mezzolombardo</t>
+          <t>Viale Martiri, Fermata autobus - Riva del Garda</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO</t>
+          <t>IS MARCONI ROVERETO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Via Piomarta c/o Palazzetto Sport - Rovereto</t>
+          <t>Via Monti, n. 1 – Rovereto, Parcheggio di fronte all'Istituto Marconi</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>IS MARTINI MEZZOLOMBARDO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Via Perlasca 4, Mezzolombardo</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IS ROSMINI ROVERETO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Via Piomarta c/o Palazzetto Sport - Rovereto</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>IS TIONE GUETTI</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Via Durone 53, Tione</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C21" t="n">
         <v>10</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Scacchi_18-feb-25_DEF/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Scacchi_18-feb-25_DEF/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,82 +436,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO – Scuola secondaria</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Via Torre Franca, fermata bus "Al Parco" - Mattarello</t>
+          <t>Pizzeria "Il Picchio" - Roncegno</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC ISERA-ROVERETO – Scuola primaria F.lli Filzi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pizzeria "Il Picchio" - Roncegno</t>
+          <t>Via Unione, 23 - Rovereto</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ISERA-ROVERETO – Scuola primaria F.lli Filzi</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Via Unione, 23 - Rovereto</t>
+          <t>Via Carlo Sette, 13/a - Lavis</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC MEZZANO SANTA CROCE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via Carlo Sette, 13/a - Lavis</t>
+          <t>Via Molaren, 29 - Mezzano</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC MEZZANO SANTA CROCE</t>
+          <t>IC ROVERETO EST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Via Molaren, 29 - Mezzano</t>
+          <t>Piazzale Achille Leoni - Rovereto</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC ROVERETO LA VELA Primaria 1°</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC ROVERETO LA VELA Primaria 1°</t>
+          <t>IC ROVERETO LA VELA Primaria 2°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -535,37 +535,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC ROVERETO LA VELA Primaria 2°</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Piazzale Achille Leoni - Rovereto</t>
+          <t>Corso Bettini 67 - Rovereto</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC ROVERETO SUD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Corso Bettini 67 - Rovereto</t>
+          <t>Via Benacense, 32 - Rovereto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -576,22 +576,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Via Benacense, 32 - Rovereto</t>
+          <t>Via Livenza 1 - Rovereto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC ROVERETO SUD</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Via Livenza 1 - Rovereto</t>
+          <t>Via Circonvalazione 44 - Tione</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -601,135 +601,120 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IS CLES PILATI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via Circonvalazione 44 - Tione</t>
+          <t>Piazza Fiera, Cles</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IS CLES PILATI</t>
+          <t>IS DON MILANI ROVERETO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Piazza Fiera, Cles</t>
+          <t>Via Balista 2, Rovereto</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IS DON MILANI ROVERETO</t>
+          <t>IS FLORIANI RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Via Balista 2, Rovereto</t>
+          <t>Viale dei Tigli, 43 - Riva del Garda</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IS FLORIANI RIVA DEL GARDA</t>
+          <t>IS MAFFEI RIVA DEL GARDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Viale dei Tigli, 43 - Riva del Garda</t>
+          <t>Viale Martiri, Fermata autobus - Riva del Garda</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IS MAFFEI RIVA DEL GARDA</t>
+          <t>IS MARCONI ROVERETO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viale Martiri, Fermata autobus - Riva del Garda</t>
+          <t>Via Monti, n. 1 – Rovereto, Parcheggio di fronte all'Istituto Marconi</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IS MARCONI ROVERETO</t>
+          <t>IS MARTINI MEZZOLOMBARDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Via Monti, n. 1 – Rovereto, Parcheggio di fronte all'Istituto Marconi</t>
+          <t>Via Perlasca 4, Mezzolombardo</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IS MARTINI MEZZOLOMBARDO</t>
+          <t>IS ROSMINI ROVERETO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Via Perlasca 4, Mezzolombardo</t>
+          <t>Via Piomarta c/o Palazzetto Sport - Rovereto</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IS ROSMINI ROVERETO</t>
+          <t>IS TIONE GUETTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Via Piomarta c/o Palazzetto Sport - Rovereto</t>
+          <t>Via Durone 53, Tione</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IS TIONE GUETTI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Via Durone 53, Tione</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
         <v>10</v>
       </c>
     </row>
